--- a/2_CATION_EXCHANGE_PROBLEM/ANALYSIS_AND_FIGURES/RESULTS_CATION_EXCHANGE_ERROR_METRICS.xlsx
+++ b/2_CATION_EXCHANGE_PROBLEM/ANALYSIS_AND_FIGURES/RESULTS_CATION_EXCHANGE_ERROR_METRICS.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METRICS_SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METRICS_AGGREGATE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METRICS_OVERALL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORST_POINT_PER_SPECIES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAIRED_POINTWISE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METRICS_BY_GROUP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METRICS_OVERALL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORST_POINT_PER_SPECIES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAIRED_POINTWISE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1093,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,25 +1120,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Mean_NRMSE_%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Mean_MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Max_AbsError</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_AbsError_DAY</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mean_R2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Mean_NSE</t>
         </is>
@@ -1159,18 +1165,21 @@
         <v>0.01156970800184151</v>
       </c>
       <c r="E2" t="n">
+        <v>2.011556873283444</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.005632426976261947</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.05785628199999998</v>
       </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
       <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.9974236476651432</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.9910760555069974</v>
       </c>
     </row>
@@ -1190,18 +1199,21 @@
         <v>0.002709144589720908</v>
       </c>
       <c r="E3" t="n">
+        <v>4.266841655538292</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.002045958175952361</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.008861833</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.9921728383048015</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.917144666825898</v>
       </c>
     </row>
@@ -1221,18 +1233,21 @@
         <v>0.02146824438546749</v>
       </c>
       <c r="E4" t="n">
+        <v>2.238306653906939</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.01372715371143652</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.1127200110000001</v>
       </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.9948217657962436</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.9941331613806285</v>
       </c>
     </row>
@@ -1252,18 +1267,21 @@
         <v>0.005662071439263311</v>
       </c>
       <c r="E5" t="n">
+        <v>18.16198197752126</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.003368381782518217</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.01190741000000006</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9994599899357163</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.3041116926979974</v>
       </c>
     </row>
@@ -1283,18 +1301,21 @@
         <v>0.01074842200046651</v>
       </c>
       <c r="E6" t="n">
+        <v>1.617565773807112</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.00912569641506928</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.02579672500000008</v>
       </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
       <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9997997623571875</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.9971332411991054</v>
       </c>
     </row>
@@ -1309,67 +1330,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Mean_RMSE</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Pooled_RMSE</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Simple_RMSE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Mean_NRMSE_%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Mean_MAE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_AbsError</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Mean_R2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Mean_NSE</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>N_pairs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0.01016576013361952</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.01202227043011812</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CATIONS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ca2+, Na+, K+</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01202227043011812</v>
+        <v>0.01488817862804693</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006779923412247665</v>
+        <v>0.01565934469435722</v>
       </c>
       <c r="E2" t="n">
+        <v>0.01565934469435722</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.955809766999165</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.009495092367589251</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.1127200110000001</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.9967356008118184</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8407197635221253</v>
+      <c r="I2" t="n">
+        <v>0.9973483919395247</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9941141526955772</v>
+      </c>
+      <c r="K2" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ANIONS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cl-, NO3-</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.003082132391978422</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.003875478884828337</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.003875478884828338</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.21441181652978</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.002707169979235289</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01190741000000006</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9958164141202589</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6106281797619477</v>
+      </c>
+      <c r="K3" t="n">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -1383,149 +1479,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Species</t>
+          <t>Mean_RMSE</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>Pooled_RMSE</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Simple_RMSE</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>REF_INTERP</t>
+          <t>Mean_NRMSE_%</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>Mean_MAE</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ABS_ERROR</t>
+          <t>Max_AbsError</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mean_R2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Mean_NSE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ca2+</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.01016576013361952</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>0.01202227043011812</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>0.01202227043011812</v>
       </c>
       <c r="D2" t="n">
-        <v>0.16715</v>
+        <v>5.659250586811409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.225006282</v>
+        <v>0.006779923412247665</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05785628199999998</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cl-</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>31</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.124995</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.133856833</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.008861833</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K+</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.802845</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.690124989</v>
-      </c>
-      <c r="F4" t="n">
         <v>0.1127200110000001</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NO3-</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>31</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.06309259</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.01190741000000006</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Na+</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5064200000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.480623275</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.02579672500000008</v>
+      <c r="G2" t="n">
+        <v>0.9967356008118184</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8407197635221253</v>
       </c>
     </row>
   </sheetData>
@@ -1539,6 +1561,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>REF_INTERP</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ABS_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ca2+</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.16715</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.225006282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05785628199999998</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cl-</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.124995</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.133856833</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.008861833</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K+</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.802845</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.690124989</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1127200110000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NO3-</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.06309259</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01190741000000006</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Na+</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5064200000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.480623275</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02579672500000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
